--- a/data/actual_data.xlsx
+++ b/data/actual_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yaolinjia/Desktop/Grape/dm_first_inf/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F46EFA2E-DEAC-FA4B-9DD0-222CD6B4EFD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C7EF0C2-2F75-854B-BCEE-4FCD35997FB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-3400" yWindow="-19580" windowWidth="25600" windowHeight="14520" xr2:uid="{F7F9E586-A793-3842-9CBF-F3C9E40254D5}"/>
+    <workbookView xWindow="-6020" yWindow="-19640" windowWidth="25600" windowHeight="14520" xr2:uid="{F7F9E586-A793-3842-9CBF-F3C9E40254D5}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="18">
   <si>
     <t>plot</t>
   </si>
@@ -90,6 +90,12 @@
   </si>
   <si>
     <t>NN</t>
+  </si>
+  <si>
+    <t>last_spore_date</t>
+  </si>
+  <si>
+    <t>year</t>
   </si>
 </sst>
 </file>
@@ -498,179 +504,223 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15F015A4-D766-CE4B-AE02-CBF6DFCC126A}">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="4" width="21.33203125" style="1" customWidth="1"/>
-    <col min="5" max="7" width="22.6640625" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="10.83203125" style="1"/>
+    <col min="1" max="5" width="21.33203125" style="1" customWidth="1"/>
+    <col min="6" max="8" width="22.6640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="I1" s="5" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="3">
+        <v>2022</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="D2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="3">
+      <c r="E2" s="3">
         <v>53</v>
       </c>
-      <c r="E2" s="4">
+      <c r="F2" s="4">
         <v>44661</v>
       </c>
-      <c r="F2" s="2">
+      <c r="G2" s="2">
         <v>44711</v>
       </c>
-      <c r="G2" s="2">
+      <c r="H2" s="2">
         <v>44668</v>
       </c>
+      <c r="I2" s="4">
+        <v>44708</v>
+      </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="3">
+        <v>2022</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="3">
+      <c r="E3" s="3">
         <v>53</v>
       </c>
-      <c r="E3" s="4">
+      <c r="F3" s="4">
         <v>44689</v>
       </c>
-      <c r="F3" s="2">
+      <c r="G3" s="2">
         <v>44689</v>
       </c>
-      <c r="G3" s="2">
+      <c r="H3" s="2">
         <v>44662</v>
       </c>
+      <c r="I3" s="4">
+        <v>44683</v>
+      </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="3">
+        <v>2023</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="D4" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="3">
+      <c r="E4" s="3">
         <v>53</v>
       </c>
-      <c r="E4" s="4">
+      <c r="F4" s="4">
         <v>45013</v>
       </c>
-      <c r="F4" s="2">
+      <c r="G4" s="2">
         <v>45074</v>
       </c>
-      <c r="G4" s="2">
+      <c r="H4" s="2">
         <v>45035</v>
       </c>
+      <c r="I4" s="4">
+        <v>45068</v>
+      </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="3">
+        <v>2024</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="D5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="3">
+      <c r="E5" s="3">
         <v>53</v>
       </c>
-      <c r="E5" s="4">
+      <c r="F5" s="4">
         <v>45394</v>
       </c>
-      <c r="F5" s="2">
+      <c r="G5" s="2">
         <v>45409</v>
       </c>
-      <c r="G5" s="2">
+      <c r="H5" s="2">
         <v>45394</v>
       </c>
+      <c r="I5" s="4">
+        <v>45403</v>
+      </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="3">
+        <v>2023</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="D6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="3">
+      <c r="E6" s="3">
         <v>55</v>
       </c>
-      <c r="E6" s="4">
+      <c r="F6" s="4">
         <v>45006</v>
       </c>
-      <c r="F6" s="2">
+      <c r="G6" s="2">
         <v>45087</v>
       </c>
-      <c r="G6" s="2">
+      <c r="H6" s="2">
         <v>45015</v>
       </c>
+      <c r="I6" s="4">
+        <v>45084</v>
+      </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="3">
+        <v>2024</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="D7" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="3">
+      <c r="E7" s="3">
         <v>53</v>
       </c>
-      <c r="E7" s="4">
+      <c r="F7" s="4">
         <v>45383</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45404</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45395</v>
       </c>
+      <c r="I7" s="4">
+        <v>45401</v>
+      </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="G8" s="2"/>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="H8" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>